--- a/docs/usage/sample_sheets/sheets_tseep.xlsx
+++ b/docs/usage/sample_sheets/sheets_tseep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807E244B-733A-DD48-859C-6A1D7FF99A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D9778-BA48-644C-980F-473DF9F954B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -458,9 +458,6 @@
     <t>nu</t>
   </si>
   <si>
-    <t>ssr_zone</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -972,6 +969,9 @@
   </si>
   <si>
     <t>corps</t>
+  </si>
+  <si>
+    <t>Mat ID = -1 --&gt; SSR reduce, Mat ID = -2 --&gt; SSR hold, Mat ID = -3 --&gt; SSR elastic</t>
   </si>
 </sst>
 </file>
@@ -1479,11 +1479,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1504,21 +1511,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8972,7 +8965,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9265,7 +9258,7 @@
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
@@ -9364,90 +9357,90 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
       <c r="F2" s="63" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="J2" s="63" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K2" s="62"/>
       <c r="L2" s="62"/>
       <c r="N2" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="R2" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
       <c r="V2" s="63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W2" s="62"/>
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
@@ -9850,12 +9843,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9876,67 +9869,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>256</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>265</v>
       </c>
       <c r="Q2" s="28" t="s">
         <v>130</v>
       </c>
       <c r="R2" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z2" t="s">
         <v>266</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>267</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>268</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -9967,13 +9960,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA3" t="s">
         <v>270</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>271</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -10004,7 +9997,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -10035,7 +10028,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -10122,13 +10115,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA8" t="s">
         <v>267</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>268</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -10159,13 +10152,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA9" t="s">
         <v>270</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>271</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -10196,13 +10189,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -10233,13 +10226,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AA11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -10603,61 +10596,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="41" t="s">
         <v>279</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>280</v>
       </c>
       <c r="N2" s="28" t="s">
         <v>130</v>
       </c>
       <c r="O2" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="P2" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>282</v>
-      </c>
       <c r="Z2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AA2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -10681,10 +10674,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AA3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -10927,22 +10920,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>179</v>
-      </c>
       <c r="E2" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -11165,27 +11158,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -11209,63 +11202,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -11294,10 +11287,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U5" t="s">
         <v>294</v>
-      </c>
-      <c r="U5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -11326,7 +11319,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -11619,27 +11612,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -11663,63 +11656,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -11748,10 +11741,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U5" t="s">
         <v>294</v>
-      </c>
-      <c r="U5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -13043,52 +13036,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:AQ52"/>
+  <dimension ref="A2:AP52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="42" width="8.5" customWidth="1"/>
+    <col min="11" max="41" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="6"/>
-      <c r="AK2" s="6" t="s">
+      <c r="AD2" s="6"/>
+      <c r="AJ2" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>91</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="P3" t="s">
         <v>93</v>
       </c>
-      <c r="AE3" s="14"/>
-      <c r="AK3" s="1" t="s">
+      <c r="AD3" s="14"/>
+      <c r="AJ3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AK3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
@@ -13099,21 +13092,21 @@
       <c r="M4" t="s">
         <v>98</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="P4" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" s="14"/>
-      <c r="AK4" s="1" t="s">
+      <c r="AD4" s="14"/>
+      <c r="AJ4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AK4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>102</v>
       </c>
@@ -13124,21 +13117,21 @@
       <c r="M5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AE5" s="14"/>
-      <c r="AK5" s="1" t="s">
+      <c r="AD5" s="14"/>
+      <c r="AJ5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AL5" s="9" t="s">
+      <c r="AK5" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
@@ -13149,26 +13142,26 @@
       <c r="M6" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="P6" t="s">
         <v>113</v>
       </c>
+      <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>115</v>
       </c>
+      <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
         <v>116</v>
       </c>
@@ -13195,18 +13188,18 @@
       <c r="X9" s="54"/>
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
-      <c r="AA9" s="54"/>
-      <c r="AB9" s="53" t="s">
+      <c r="AA9" s="53" t="s">
         <v>117</v>
       </c>
+      <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
       <c r="AD9" s="54"/>
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
-      <c r="AG9" s="54"/>
-      <c r="AH9" s="53" t="s">
+      <c r="AG9" s="53" t="s">
         <v>118</v>
       </c>
+      <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
       <c r="AJ9" s="54"/>
       <c r="AK9" s="54"/>
@@ -13215,9 +13208,8 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-      <c r="AQ9" s="54"/>
-    </row>
-    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
@@ -13260,14 +13252,14 @@
       <c r="N10" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="O10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>132</v>
       </c>
       <c r="P10" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>133</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>112</v>
       </c>
       <c r="R10" s="44" t="s">
         <v>134</v>
@@ -13296,25 +13288,25 @@
       <c r="Z10" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="AA10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
         <v>143</v>
       </c>
       <c r="AB10" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="AC10" s="46" t="s">
+      <c r="AC10" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AD10" s="47" t="s">
+      <c r="AD10" s="46" t="s">
         <v>146</v>
       </c>
       <c r="AE10" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="AF10" s="46" t="s">
+      <c r="AF10" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="AG10" s="47" t="s">
+      <c r="AG10" s="23" t="s">
         <v>149</v>
       </c>
       <c r="AH10" s="23" t="s">
@@ -13344,11 +13336,8 @@
       <c r="AP10" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="AQ10" s="23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -13391,17 +13380,19 @@
       <c r="N11" s="3">
         <v>0.2</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>seep</t>
         </is>
       </c>
-      <c r="Q11" s="3">
+      <c r="P11" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
+      <c r="S11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T11" s="3">
         <v>0.0</v>
       </c>
@@ -13442,42 +13433,39 @@
         <v>0.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="AH11" s="3">
         <v>1.0</v>
       </c>
       <c r="AI11" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="AJ11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AK11" s="3" t="inlineStr">
+      <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK11" s="3">
+        <v>0.0001</v>
+      </c>
       <c r="AL11" s="3">
-        <v>0.0001</v>
+        <v>-1.0</v>
       </c>
       <c r="AM11" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.0</v>
+        <v>1e-05</v>
       </c>
       <c r="AP11" s="3">
-        <v>1e-05</v>
-      </c>
-      <c r="AQ11" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -13520,17 +13508,19 @@
       <c r="N12" s="3">
         <v>0.4</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>seep</t>
         </is>
       </c>
-      <c r="Q12" s="3">
+      <c r="P12" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
+      <c r="S12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T12" s="3">
         <v>0.0</v>
       </c>
@@ -13571,42 +13561,39 @@
         <v>0.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0</v>
+        <v>0.001</v>
       </c>
       <c r="AH12" s="3">
         <v>0.001</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AJ12" s="3">
         <v>0.0</v>
       </c>
-      <c r="AK12" s="3" t="inlineStr">
+      <c r="AJ12" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK12" s="3">
+        <v>0.0001</v>
+      </c>
       <c r="AL12" s="3">
-        <v>0.0001</v>
-      </c>
-      <c r="AM12" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AN12" s="18">
+      <c r="AM12" s="18">
         <v>0.0</v>
       </c>
+      <c r="AN12" s="19">
+        <v>0.0</v>
+      </c>
       <c r="AO12" s="19">
-        <v>0.0</v>
+        <v>1e-05</v>
       </c>
       <c r="AP12" s="19">
-        <v>1e-05</v>
-      </c>
-      <c r="AQ12" s="19">
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -13649,17 +13636,19 @@
       <c r="N13" s="3">
         <v>0.35</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>seep</t>
         </is>
       </c>
-      <c r="Q13" s="3">
+      <c r="P13" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
+      <c r="S13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T13" s="3">
         <v>0.0</v>
       </c>
@@ -13700,42 +13689,39 @@
         <v>0.0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
       <c r="AH13" s="3">
         <v>0.1</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="AJ13" s="3">
         <v>0.0</v>
       </c>
-      <c r="AK13" s="3" t="inlineStr">
+      <c r="AJ13" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK13" s="3">
+        <v>0.0001</v>
+      </c>
       <c r="AL13" s="3">
-        <v>0.0001</v>
-      </c>
-      <c r="AM13" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AN13" s="18">
+      <c r="AM13" s="18">
         <v>0.0</v>
       </c>
+      <c r="AN13" s="19">
+        <v>0.0</v>
+      </c>
       <c r="AO13" s="19">
-        <v>0.0</v>
+        <v>1e-05</v>
       </c>
       <c r="AP13" s="19">
-        <v>1e-05</v>
-      </c>
-      <c r="AQ13" s="19">
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -13780,9 +13766,8 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-      <c r="AQ14" s="3"/>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -13827,9 +13812,8 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-    </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -13874,9 +13858,8 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -13921,9 +13904,8 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -13968,9 +13950,8 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -14015,9 +13996,8 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -14062,9 +14042,8 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -14109,9 +14088,8 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -14156,9 +14134,8 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-      <c r="AQ22" s="3"/>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -14203,9 +14180,8 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-      <c r="AQ23" s="3"/>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -14250,9 +14226,8 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-      <c r="AQ24" s="3"/>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -14297,9 +14272,8 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-      <c r="AQ25" s="3"/>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -14332,9 +14306,8 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-      <c r="AQ26" s="1"/>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -14357,9 +14330,8 @@
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -14382,9 +14354,8 @@
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -14407,9 +14378,8 @@
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -14432,9 +14402,8 @@
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -14457,9 +14426,8 @@
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14482,9 +14450,8 @@
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
-    </row>
-    <row r="33" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -14507,9 +14474,8 @@
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="1"/>
-    </row>
-    <row r="34" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -14532,9 +14498,8 @@
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-    </row>
-    <row r="35" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -14557,9 +14522,8 @@
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
-    </row>
-    <row r="36" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -14582,9 +14546,8 @@
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-    </row>
-    <row r="37" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -14607,9 +14570,8 @@
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-    </row>
-    <row r="38" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -14632,9 +14594,8 @@
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
-    </row>
-    <row r="39" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -14657,9 +14618,8 @@
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
-      <c r="AG39" s="1"/>
-    </row>
-    <row r="40" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -14682,9 +14642,8 @@
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AG40" s="1"/>
-    </row>
-    <row r="41" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -14707,9 +14666,8 @@
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AG41" s="1"/>
-    </row>
-    <row r="42" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -14732,9 +14690,8 @@
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-    </row>
-    <row r="43" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -14757,9 +14714,8 @@
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
-    </row>
-    <row r="44" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -14782,9 +14738,8 @@
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-    </row>
-    <row r="45" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -14807,9 +14762,8 @@
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-    </row>
-    <row r="46" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -14832,9 +14786,8 @@
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
-    </row>
-    <row r="47" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -14857,9 +14810,8 @@
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
-      <c r="AG47" s="1"/>
-    </row>
-    <row r="48" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -14882,9 +14834,8 @@
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
-      <c r="AG48" s="1"/>
-    </row>
-    <row r="49" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -14907,9 +14858,8 @@
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AG49" s="1"/>
-    </row>
-    <row r="50" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -14932,9 +14882,8 @@
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
-    </row>
-    <row r="51" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -14957,9 +14906,8 @@
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AG51" s="1"/>
-    </row>
-    <row r="52" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -14982,109 +14930,103 @@
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C9:AA9"/>
-    <mergeCell ref="AB9:AG9"/>
-    <mergeCell ref="AH9:AQ9"/>
+    <mergeCell ref="C9:Z9"/>
+    <mergeCell ref="AA9:AF9"/>
+    <mergeCell ref="AG9:AP9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11:K52 AC11:AG52">
-    <cfRule type="expression" dxfId="20" priority="6">
+  <conditionalFormatting sqref="F11:K52 AB11:AF52">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="18" priority="7">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:L52">
-    <cfRule type="expression" dxfId="18" priority="19">
+  <conditionalFormatting sqref="F11:L52 O11:R52">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="17" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="15" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:S52">
-    <cfRule type="expression" dxfId="14" priority="4">
+  <conditionalFormatting sqref="P11:P52">
+    <cfRule type="expression" dxfId="13" priority="13">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S11:V52">
+    <cfRule type="expression" dxfId="12" priority="11">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W11:Z52">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB11:AF52">
+    <cfRule type="expression" dxfId="10" priority="21">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:Q52">
-    <cfRule type="expression" dxfId="13" priority="13">
-      <formula>AND($P11&lt;&gt;"",$P11&lt;&gt;"ru")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R11:S52">
-    <cfRule type="expression" dxfId="12" priority="3">
+  <conditionalFormatting sqref="AC11:AC52">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>$E11="cp"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="5">
-      <formula>AND($P11&lt;&gt;"",$P11&lt;&gt;"piezo",$P11&lt;&gt;"seep")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T11:W52">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X11:AA52">
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC11:AG52">
-    <cfRule type="expression" dxfId="8" priority="21">
-      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD52">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>$E11="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE11:AF52">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE11:AE52">
-    <cfRule type="expression" dxfId="6" priority="15">
-      <formula>$E11="mc"</formula>
+  <conditionalFormatting sqref="AK11:AL52">
+    <cfRule type="expression" dxfId="6" priority="17">
+      <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF11:AG52">
-    <cfRule type="expression" dxfId="5" priority="16">
+  <conditionalFormatting sqref="AM11:AN52">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$AJ11="lf"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="1" priority="23">
       <formula>$E11="cp"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL11:AM52">
-    <cfRule type="expression" dxfId="4" priority="17">
-      <formula>OR($AK11="vg",$AK11="gard")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN11:AO52">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$AK11="lf"</formula>
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="E11:E52" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$C$3:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AK11:AK102" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>$AK$3:$AK$5</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="AJ11:AJ102" xr:uid="{00000000-0002-0000-0200-000001000000}">
+      <formula1>$AJ$3:$AJ$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="P11:P52" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>$P$3:$P$6</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="O11:O52" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>$O$3:$O$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15119,13 +15061,13 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -15148,157 +15090,157 @@
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -15391,102 +15333,102 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="J7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="M7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="P7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="AE7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
@@ -16351,6 +16293,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -16367,20 +16323,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16414,174 +16356,177 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="39">
         <v>1</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E5" s="39">
         <v>2</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="39">
         <v>3</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K5" s="39">
         <v>4</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N5" s="39">
         <v>5</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="39">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T5" s="39">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W5" s="39">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z5" s="39">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AC5" s="39">
         <v>10</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF5" s="39">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI5" s="39">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL5" s="39">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO5" s="39">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR5" s="39">
         <v>15</v>
@@ -16589,187 +16534,187 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(B5=-1,"SSR reduce",IF(B5=-2,"SSR hold",IF(B5=-3,"SSR elastic",_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(E5=-1,"SSR reduce",IF(E5=-2,"SSR hold",IF(E5=-3,"SSR elastic",_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="E6" s="57"/>
       <c r="G6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(H5=-1,"SSR reduce",IF(H5=-2,"SSR hold",IF(H5=-3,"SSR elastic",_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="H6" s="57"/>
       <c r="J6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(K5=-1,"SSR reduce",IF(K5=-2,"SSR hold",IF(K5=-3,"SSR elastic",_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="K6" s="57"/>
       <c r="M6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(N5=-1,"SSR reduce",IF(N5=-2,"SSR hold",IF(N5=-3,"SSR elastic",_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="N6" s="57"/>
       <c r="P6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(Q5=-1,"SSR reduce",IF(Q5=-2,"SSR hold",IF(Q5=-3,"SSR elastic",_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="Q6" s="57"/>
       <c r="R6" s="1"/>
       <c r="S6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(T5=-1,"SSR reduce",IF(T5=-2,"SSR hold",IF(T5=-3,"SSR elastic",_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="T6" s="57"/>
       <c r="U6" s="1"/>
       <c r="V6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(W5=-1,"SSR reduce",IF(W5=-2,"SSR hold",IF(W5=-3,"SSR elastic",_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="W6" s="57"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(Z5=-1,"SSR reduce",IF(Z5=-2,"SSR hold",IF(Z5=-3,"SSR elastic",_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="Z6" s="57"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AC5=-1,"SSR reduce",IF(AC5=-2,"SSR hold",IF(AC5=-3,"SSR elastic",_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AC6" s="57"/>
       <c r="AE6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AF5=-1,"SSR reduce",IF(AF5=-2,"SSR hold",IF(AF5=-3,"SSR elastic",_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AF6" s="57"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AI5=-1,"SSR reduce",IF(AI5=-2,"SSR hold",IF(AI5=-3,"SSR elastic",_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AI6" s="57"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AL5=-1,"SSR reduce",IF(AL5=-2,"SSR hold",IF(AL5=-3,"SSR elastic",_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AL6" s="57"/>
       <c r="AM6" s="1"/>
       <c r="AN6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AO5=-1,"SSR reduce",IF(AO5=-2,"SSR hold",IF(AO5=-3,"SSR elastic",_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AO6" s="57"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AR5=-1,"SSR reduce",IF(AR5=-2,"SSR hold",IF(AR5=-3,"SSR elastic",_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="J7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="M7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="P7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="AE7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
@@ -17574,6 +17519,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -17590,20 +17549,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17620,20 +17565,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -17641,7 +17586,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -17652,19 +17597,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -17677,7 +17622,7 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -17686,10 +17631,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" t="s">
         <v>202</v>
-      </c>
-      <c r="H6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -17826,31 +17771,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>16</v>
@@ -17878,10 +17823,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -17896,10 +17841,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -17914,10 +17859,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" t="s">
         <v>216</v>
-      </c>
-      <c r="K5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -17944,7 +17889,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -17959,7 +17904,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K8"/>
     </row>
@@ -17975,7 +17920,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K9"/>
     </row>
@@ -17991,7 +17936,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K10"/>
     </row>
@@ -18007,7 +17952,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K11"/>
     </row>
@@ -18023,31 +17968,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -18056,23 +18001,23 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18097,16 +18042,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>231</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>16</v>
@@ -18117,10 +18062,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" t="s">
         <v>232</v>
-      </c>
-      <c r="F3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -18128,10 +18073,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" t="s">
         <v>234</v>
-      </c>
-      <c r="F4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -18139,10 +18084,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" t="s">
         <v>236</v>
-      </c>
-      <c r="F5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -18266,90 +18211,90 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
       <c r="F2" s="61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="J2" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K2" s="62"/>
       <c r="L2" s="62"/>
       <c r="N2" s="61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="R2" s="61" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
       <c r="V2" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W2" s="62"/>
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
@@ -18752,12 +18697,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/usage/sample_sheets/sheets_tseep.xlsx
+++ b/docs/usage/sample_sheets/sheets_tseep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D9778-BA48-644C-980F-473DF9F954B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEB53F3-5E86-5B42-A7B6-55B20E1E8D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="310">
   <si>
     <t>time</t>
   </si>
@@ -971,7 +971,25 @@
     <t>corps</t>
   </si>
   <si>
-    <t>Mat ID = -1 --&gt; SSR reduce, Mat ID = -2 --&gt; SSR hold, Mat ID = -3 --&gt; SSR elastic</t>
+    <t>Size:</t>
+  </si>
+  <si>
+    <t>Direction:</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>Type: material zone (default), an SSR analysis overlay, or a mesh refinement region.   Size: optional target mesh element size inside the polygon (blank = global size).</t>
+  </si>
+  <si>
+    <t>Side BC:</t>
+  </si>
+  <si>
+    <t>rollers</t>
+  </si>
+  <si>
+    <t>Size: optional target mesh element size inside this line's material zone (blank = global size).</t>
   </si>
 </sst>
 </file>
@@ -1479,18 +1497,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="35">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1511,7 +1522,119 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1686,7 +1809,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$A$8:$A$27</c:f>
+              <c:f>profile!$A$9:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1695,7 +1818,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$B$8:$B$27</c:f>
+              <c:f>profile!$B$9:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1749,7 +1872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$D$8:$D$27</c:f>
+              <c:f>profile!$D$9:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1758,7 +1881,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$E$8:$E$27</c:f>
+              <c:f>profile!$E$9:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1812,7 +1935,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$G$8:$G$27</c:f>
+              <c:f>profile!$G$9:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1821,7 +1944,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$H$8:$H$27</c:f>
+              <c:f>profile!$H$9:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1875,7 +1998,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$J$8:$J$27</c:f>
+              <c:f>profile!$J$9:$J$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1884,7 +2007,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$K$8:$K$27</c:f>
+              <c:f>profile!$K$9:$K$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1938,7 +2061,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$M$8:$M$27</c:f>
+              <c:f>profile!$M$9:$M$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1947,7 +2070,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$N$8:$N$27</c:f>
+              <c:f>profile!$N$9:$N$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2001,7 +2124,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$P$8:$P$27</c:f>
+              <c:f>profile!$P$9:$P$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2010,7 +2133,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Q$8:$Q$27</c:f>
+              <c:f>profile!$Q$9:$Q$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2070,7 +2193,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$S$8:$S$27</c:f>
+              <c:f>profile!$S$9:$S$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2079,7 +2202,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$T$8:$T$27</c:f>
+              <c:f>profile!$T$9:$T$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2139,7 +2262,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$V$8:$V$27</c:f>
+              <c:f>profile!$V$9:$V$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2148,7 +2271,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$W$8:$W$27</c:f>
+              <c:f>profile!$W$9:$W$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2208,7 +2331,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$Y$8:$Y$27</c:f>
+              <c:f>profile!$Y$9:$Y$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2217,7 +2340,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Z$8:$Z$27</c:f>
+              <c:f>profile!$Z$9:$Z$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2277,7 +2400,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AB$8:$AB$27</c:f>
+              <c:f>profile!$AB$9:$AB$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2286,7 +2409,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AC$8:$AC$27</c:f>
+              <c:f>profile!$AC$9:$AC$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2346,7 +2469,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AE$8:$AE$27</c:f>
+              <c:f>profile!$AE$9:$AE$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2355,7 +2478,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AF$8:$AF$27</c:f>
+              <c:f>profile!$AF$9:$AF$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2415,7 +2538,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AH$8:$AH$27</c:f>
+              <c:f>profile!$AH$9:$AH$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2424,7 +2547,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AI$8:$AI$27</c:f>
+              <c:f>profile!$AI$9:$AI$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2484,7 +2607,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AK$8:$AK$27</c:f>
+              <c:f>profile!$AK$9:$AK$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2493,7 +2616,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AL$8:$AL$27</c:f>
+              <c:f>profile!$AL$9:$AL$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2556,7 +2679,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AN$8:$AN$27</c:f>
+              <c:f>profile!$AN$9:$AN$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2565,7 +2688,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AO$8:$AO$27</c:f>
+              <c:f>profile!$AO$9:$AO$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2628,7 +2751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AQ$8:$AQ$27</c:f>
+              <c:f>profile!$AQ$9:$AQ$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2637,7 +2760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AR$8:$AR$27</c:f>
+              <c:f>profile!$AR$9:$AR$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2879,7 +3002,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$B$4:$B$13</c:f>
+              <c:f>dloads!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2888,7 +3011,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$C$4:$C$13</c:f>
+              <c:f>dloads!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2951,7 +3074,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$F$4:$F$13</c:f>
+              <c:f>dloads!$F$5:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2960,7 +3083,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$G$4:$G$13</c:f>
+              <c:f>dloads!$G$5:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3023,7 +3146,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$J$4:$J$13</c:f>
+              <c:f>dloads!$J$5:$J$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3032,7 +3155,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$K$4:$K$13</c:f>
+              <c:f>dloads!$K$5:$K$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3095,7 +3218,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$N$4:$N$13</c:f>
+              <c:f>dloads!$N$5:$N$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3104,7 +3227,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$O$4:$O$13</c:f>
+              <c:f>dloads!$O$5:$O$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3167,7 +3290,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$R$4:$R$22</c:f>
+              <c:f>dloads!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3176,7 +3299,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$S$4:$S$22</c:f>
+              <c:f>dloads!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3239,7 +3362,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$V$4:$V$22</c:f>
+              <c:f>dloads!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3248,7 +3371,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$W$4:$W$22</c:f>
+              <c:f>dloads!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3496,7 +3619,7 @@
           </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$B$4:$B$22</c:f>
+              <c:f>'dloads (2)'!$B$5:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3505,7 +3628,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$C$4:$C$22</c:f>
+              <c:f>'dloads (2)'!$C$5:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3565,7 +3688,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$F$4:$F$22</c:f>
+              <c:f>'dloads (2)'!$F$5:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3574,7 +3697,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$G$4:$G$22</c:f>
+              <c:f>'dloads (2)'!$G$5:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3628,7 +3751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$J$4:$J$22</c:f>
+              <c:f>'dloads (2)'!$J$5:$J$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3637,7 +3760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$K$4:$K$22</c:f>
+              <c:f>'dloads (2)'!$K$5:$K$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3691,7 +3814,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$N$4:$N$22</c:f>
+              <c:f>'dloads (2)'!$N$5:$N$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3700,7 +3823,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$O$4:$O$22</c:f>
+              <c:f>'dloads (2)'!$O$5:$O$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3754,7 +3877,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$R$4:$R$22</c:f>
+              <c:f>'dloads (2)'!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3763,7 +3886,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$S$4:$S$22</c:f>
+              <c:f>'dloads (2)'!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3817,7 +3940,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$V$4:$V$22</c:f>
+              <c:f>'dloads (2)'!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3826,7 +3949,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$W$4:$W$22</c:f>
+              <c:f>'dloads (2)'!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -6241,7 +6364,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$A$8:$A$27</c:f>
+              <c:f>polygon!$A$10:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6250,7 +6373,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$B$8:$B$27</c:f>
+              <c:f>polygon!$B$10:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6310,7 +6433,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$D$8:$D$27</c:f>
+              <c:f>polygon!$D$10:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6319,7 +6442,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$E$8:$E$27</c:f>
+              <c:f>polygon!$E$10:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6379,7 +6502,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$G$8:$G$27</c:f>
+              <c:f>polygon!$G$10:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6388,7 +6511,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$H$8:$H$27</c:f>
+              <c:f>polygon!$H$10:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6448,7 +6571,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$J$8:$J$27</c:f>
+              <c:f>polygon!$J$10:$J$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6457,7 +6580,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$K$8:$K$27</c:f>
+              <c:f>polygon!$K$10:$K$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6520,7 +6643,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$M$8:$M$27</c:f>
+              <c:f>polygon!$M$10:$M$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6529,7 +6652,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$N$8:$N$27</c:f>
+              <c:f>polygon!$N$10:$N$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6592,7 +6715,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$P$8:$P$27</c:f>
+              <c:f>polygon!$P$10:$P$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6601,7 +6724,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Q$8:$Q$27</c:f>
+              <c:f>polygon!$Q$10:$Q$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6664,7 +6787,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$S$8:$S$27</c:f>
+              <c:f>polygon!$S$10:$S$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6673,7 +6796,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$T$8:$T$27</c:f>
+              <c:f>polygon!$T$10:$T$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6736,7 +6859,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$V$8:$V$27</c:f>
+              <c:f>polygon!$V$10:$V$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6745,7 +6868,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$W$8:$W$27</c:f>
+              <c:f>polygon!$W$10:$W$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6808,7 +6931,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$Y$8:$Y$27</c:f>
+              <c:f>polygon!$Y$10:$Y$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6817,7 +6940,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Z$8:$Z$27</c:f>
+              <c:f>polygon!$Z$10:$Z$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6880,7 +7003,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AB$8:$AB$27</c:f>
+              <c:f>polygon!$AB$10:$AB$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6889,7 +7012,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AC$8:$AC$27</c:f>
+              <c:f>polygon!$AC$10:$AC$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6949,7 +7072,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AE$8:$AE$27</c:f>
+              <c:f>polygon!$AE$10:$AE$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6958,7 +7081,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AF$8:$AF$27</c:f>
+              <c:f>polygon!$AF$10:$AF$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7018,7 +7141,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AH$8:$AH$27</c:f>
+              <c:f>polygon!$AH$10:$AH$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7027,7 +7150,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AI$8:$AI$27</c:f>
+              <c:f>polygon!$AI$10:$AI$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7087,7 +7210,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AK$8:$AK$27</c:f>
+              <c:f>polygon!$AK$10:$AK$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7096,7 +7219,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AL$8:$AL$27</c:f>
+              <c:f>polygon!$AL$10:$AL$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7156,7 +7279,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AN$8:$AN$27</c:f>
+              <c:f>polygon!$AN$10:$AN$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7165,7 +7288,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AO$8:$AO$27</c:f>
+              <c:f>polygon!$AO$10:$AO$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7225,7 +7348,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AQ$8:$AQ$27</c:f>
+              <c:f>polygon!$AQ$10:$AQ$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7234,7 +7357,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AR$8:$AR$27</c:f>
+              <c:f>polygon!$AR$10:$AR$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -8965,7 +9088,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="30">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9168,6 +9291,10 @@
       <c r="D21"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C22" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>62</v>
       </c>
@@ -9315,20 +9442,23 @@
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{4E2B12C7-FE67-3B4F-885D-33F99F4A0D82}">
+      <formula1>"rollers,fixed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{0D3EDF25-93C5-C944-8126-8CC9B17A21FC}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{4694A1A0-8B80-B646-8FBE-EF2E498B980D}">
       <formula1>$D$54:$D$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{0356D3C6-ECF7-2D4C-8DB0-E3BFC9D663DB}">
       <formula1>$D$60:$D$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{BDB1B4FF-9C3D-5F43-BB1B-429406E4C3E1}">
       <formula1>$D$64:$D$71</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{8A75E61B-C3DC-0F4A-869A-1DA1855E5B34}">
       <formula1>$D$74:$D$78</formula1>
     </dataValidation>
   </dataValidations>
@@ -9338,7 +9468,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -9388,90 +9518,96 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>624.0</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
-        <v>200.0</v>
+        <v>0.0</v>
       </c>
       <c r="C5" s="3">
         <v>100.0</v>
@@ -9497,13 +9633,13 @@
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
-        <v>220.0</v>
+        <v>200.0</v>
       </c>
       <c r="C6" s="3">
-        <v>110.0</v>
+        <v>100.0</v>
       </c>
       <c r="D6" s="3">
-        <v>0.0</v>
+        <v>624.0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -9522,9 +9658,15 @@
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.0</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -9841,15 +9983,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0900-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14938,84 +15111,84 @@
     <mergeCell ref="AG9:AP9"/>
   </mergeCells>
   <conditionalFormatting sqref="F11:K52 AB11:AF52">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:L52 O11:R52">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="31" priority="8">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="29" priority="10">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P52">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="27" priority="23">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S11:V52">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W11:Z52">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="24" priority="12">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB11:AF52">
-    <cfRule type="expression" dxfId="10" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC52">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="22" priority="14">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD52">
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="21" priority="15">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE11:AF52">
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="20" priority="16">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK11:AL52">
-    <cfRule type="expression" dxfId="6" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM11:AN52">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:R52">
-    <cfRule type="expression" dxfId="1" priority="23">
-      <formula>$E11="cp"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="24">
-      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -15035,7 +15208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:AR27"/>
+  <dimension ref="A2:AR28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -15069,6 +15242,9 @@
       <c r="D2" s="24" t="s">
         <v>160</v>
       </c>
+      <c r="N2" s="24" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="inlineStr">
@@ -15332,172 +15508,190 @@
       <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="37"/>
+      <c r="D7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="G7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="J7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="M7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="N7" s="37"/>
+      <c r="P7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="T7" s="37"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="W7" s="37"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC7" s="37"/>
+      <c r="AE7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR7" s="37"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
+      <c r="R8" s="1"/>
+      <c r="S8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="U8" s="1"/>
+      <c r="V8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
+      <c r="X8" s="1"/>
+      <c r="Y8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AE8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AI8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AR8" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="B8" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>320.0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="17"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="16"/>
-      <c r="AR8" s="17"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="B9" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="D9" s="3">
         <v>320.0</v>
       </c>
-      <c r="B9" s="3">
-        <v>160.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>360.0</v>
-      </c>
       <c r="E9" s="3">
-        <v>165.0</v>
+        <v>100.0</v>
       </c>
       <c r="G9" s="3">
-        <v>320.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" s="3">
         <v>100.0</v>
@@ -15509,50 +15703,50 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="19"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="17"/>
       <c r="U9" s="1"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="19"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="17"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="19"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="17"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="19"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="17"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="1"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="19"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="17"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="19"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="17"/>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="19"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="17"/>
       <c r="AP9" s="1"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="19"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="17"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
+        <v>320.0</v>
+      </c>
+      <c r="B10" s="3">
+        <v>160.0</v>
+      </c>
+      <c r="D10" s="3">
         <v>360.0</v>
-      </c>
-      <c r="B10" s="3">
-        <v>180.0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>380.0</v>
       </c>
       <c r="E10" s="3">
         <v>165.0</v>
       </c>
       <c r="G10" s="3">
-        <v>360.0</v>
+        <v>320.0</v>
       </c>
       <c r="H10" s="3">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -15589,19 +15783,19 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>380.0</v>
+        <v>360.0</v>
       </c>
       <c r="B11" s="3">
         <v>180.0</v>
       </c>
       <c r="D11" s="3">
-        <v>420.0</v>
+        <v>380.0</v>
       </c>
       <c r="E11" s="3">
-        <v>100.0</v>
+        <v>165.0</v>
       </c>
       <c r="G11" s="3">
-        <v>380.0</v>
+        <v>360.0</v>
       </c>
       <c r="H11" s="3">
         <v>60.0</v>
@@ -15616,8 +15810,8 @@
       <c r="S11" s="18"/>
       <c r="T11" s="19"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="17"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="19"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="18"/>
       <c r="Z11" s="19"/>
@@ -15641,19 +15835,1391 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
+        <v>380.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>420.0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>380.0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="19"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="18"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="1"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="19"/>
+    </row>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>550.0</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B13" s="3">
         <v>100.0</v>
       </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="G13" s="3">
+        <v>420.0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="1"/>
+      <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+    </row>
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="G14" s="3">
+        <v>750.0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="1"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="3"/>
+      <c r="AO14" s="3"/>
+      <c r="AP14" s="1"/>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="1"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="1"/>
+      <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="3"/>
+      <c r="AO17" s="3"/>
+      <c r="AP17" s="1"/>
+      <c r="AQ17" s="3"/>
+      <c r="AR17" s="3"/>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="1"/>
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="1"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="3"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="3"/>
+      <c r="AO20" s="3"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="3"/>
+      <c r="AR20" s="3"/>
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="3"/>
+      <c r="AL21" s="3"/>
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="3"/>
+      <c r="AO21" s="3"/>
+      <c r="AP21" s="1"/>
+      <c r="AQ21" s="3"/>
+      <c r="AR21" s="3"/>
+    </row>
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="3"/>
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="1"/>
+      <c r="AN22" s="3"/>
+      <c r="AO22" s="3"/>
+      <c r="AP22" s="1"/>
+      <c r="AQ22" s="3"/>
+      <c r="AR22" s="3"/>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="3"/>
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="3"/>
+      <c r="AO23" s="3"/>
+      <c r="AP23" s="1"/>
+      <c r="AQ23" s="3"/>
+      <c r="AR23" s="3"/>
+    </row>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="3"/>
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="3"/>
+      <c r="AO24" s="3"/>
+      <c r="AP24" s="1"/>
+      <c r="AQ24" s="3"/>
+      <c r="AR24" s="3"/>
+    </row>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="1"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="1"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+    </row>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="3"/>
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="3"/>
+      <c r="AO26" s="3"/>
+      <c r="AP26" s="1"/>
+      <c r="AQ26" s="3"/>
+      <c r="AR26" s="3"/>
+    </row>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="3"/>
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="3"/>
+      <c r="AO27" s="3"/>
+      <c r="AP27" s="1"/>
+      <c r="AQ27" s="3"/>
+      <c r="AR27" s="3"/>
+    </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="P6:Q6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A2:AR29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.83203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.83203125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="10.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="3.83203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="10.83203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="3.83203125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="3.83203125" customWidth="1"/>
+    <col min="18" max="18" width="3.83203125" customWidth="1"/>
+    <col min="21" max="21" width="3.83203125" customWidth="1"/>
+    <col min="24" max="24" width="3.83203125" customWidth="1"/>
+    <col min="27" max="27" width="3.83203125" customWidth="1"/>
+    <col min="30" max="30" width="3.83203125" customWidth="1"/>
+    <col min="33" max="33" width="3.83203125" customWidth="1"/>
+    <col min="36" max="36" width="3.83203125" customWidth="1"/>
+    <col min="39" max="39" width="3.83203125" customWidth="1"/>
+    <col min="42" max="42" width="3.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A2" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A4" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="D4" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="52"/>
+      <c r="G4" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="52"/>
+      <c r="J4" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="K4" s="52"/>
+      <c r="M4" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="N4" s="52"/>
+      <c r="P4" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="T4" s="54"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="W4" s="54"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC4" s="54"/>
+      <c r="AE4" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL4" s="54"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="AR4" s="54"/>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="K5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="M5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="N5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="P5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="T5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="W5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AF5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AI5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AL5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AO5" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR5" s="39" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="39">
+        <v>1</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="39">
+        <v>2</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="39">
+        <v>3</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="K6" s="39">
+        <v>4</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="N6" s="39">
+        <v>5</v>
+      </c>
+      <c r="P6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>6</v>
+      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="T6" s="39">
+        <v>7</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="V6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="W6" s="39">
+        <v>8</v>
+      </c>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z6" s="39">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC6" s="39">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF6" s="39">
+        <v>11</v>
+      </c>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI6" s="39">
+        <v>12</v>
+      </c>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL6" s="39">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO6" s="39">
+        <v>14</v>
+      </c>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR6" s="39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A7" s="58" t="str">
+        <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="B7" s="57"/>
+      <c r="D7" s="58" t="str">
+        <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="G7" s="58" t="str">
+        <f>IF(OR(H5="",H5="material"),_xlfn.XLOOKUP(H6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="H7" s="57"/>
+      <c r="J7" s="58" t="str">
+        <f>IF(OR(K5="",K5="material"),_xlfn.XLOOKUP(K6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="K7" s="57"/>
+      <c r="M7" s="58" t="str">
+        <f>IF(OR(N5="",N5="material"),_xlfn.XLOOKUP(N6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="N7" s="57"/>
+      <c r="P7" s="58" t="str">
+        <f>IF(OR(Q5="",Q5="material"),_xlfn.XLOOKUP(Q6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="58" t="str">
+        <f>IF(OR(T5="",T5="material"),_xlfn.XLOOKUP(T6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="T7" s="57"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="58" t="str">
+        <f>IF(OR(W5="",W5="material"),_xlfn.XLOOKUP(W6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="W7" s="57"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="58" t="str">
+        <f>IF(OR(Z5="",Z5="material"),_xlfn.XLOOKUP(Z6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="58" t="str">
+        <f>IF(OR(AC5="",AC5="material"),_xlfn.XLOOKUP(AC6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AC7" s="57"/>
+      <c r="AE7" s="58" t="str">
+        <f>IF(OR(AF5="",AF5="material"),_xlfn.XLOOKUP(AF6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="58" t="str">
+        <f>IF(OR(AI5="",AI5="material"),_xlfn.XLOOKUP(AI6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AI7" s="57"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="58" t="str">
+        <f>IF(OR(AL5="",AL5="material"),_xlfn.XLOOKUP(AL6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AL7" s="57"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="58" t="str">
+        <f>IF(OR(AO5="",AO5="material"),_xlfn.XLOOKUP(AO6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AO7" s="57"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="58" t="str">
+        <f>IF(OR(AR5="",AR5="material"),_xlfn.XLOOKUP(AR6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AR7" s="57"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="D8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="G8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" s="39"/>
+      <c r="J8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="M8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="N8" s="39"/>
+      <c r="P8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="W8" s="39"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC8" s="39"/>
+      <c r="AE8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR8" s="39"/>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="V9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="1"/>
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="1"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="1"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+    </row>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="G12" s="3">
-        <v>420.0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="M12" s="3"/>
@@ -15692,12 +17258,8 @@
       <c r="B13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="G13" s="3">
-        <v>750.0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>100.0</v>
-      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="M13" s="3"/>
@@ -16291,1265 +17853,199 @@
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
     </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:AR27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.83203125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.83203125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.83203125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="10.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.83203125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="10.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="3.83203125" customWidth="1"/>
-    <col min="18" max="18" width="3.83203125" customWidth="1"/>
-    <col min="21" max="21" width="3.83203125" customWidth="1"/>
-    <col min="24" max="24" width="3.83203125" customWidth="1"/>
-    <col min="27" max="27" width="3.83203125" customWidth="1"/>
-    <col min="30" max="30" width="3.83203125" customWidth="1"/>
-    <col min="33" max="33" width="3.83203125" customWidth="1"/>
-    <col min="36" max="36" width="3.83203125" customWidth="1"/>
-    <col min="39" max="39" width="3.83203125" customWidth="1"/>
-    <col min="42" max="42" width="3.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="W4" s="54"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC4" s="54"/>
-      <c r="AE4" s="55" t="s">
-        <v>190</v>
-      </c>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL4" s="54"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="55" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO4" s="54"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="55" t="s">
-        <v>194</v>
-      </c>
-      <c r="AR4" s="54"/>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="39">
-        <v>1</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="39">
-        <v>2</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="39">
-        <v>3</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="K5" s="39">
-        <v>4</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="N5" s="39">
-        <v>5</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q5" s="39">
-        <v>6</v>
-      </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="T5" s="39">
-        <v>7</v>
-      </c>
-      <c r="U5" s="1"/>
-      <c r="V5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="W5" s="39">
-        <v>8</v>
-      </c>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z5" s="39">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC5" s="39">
-        <v>10</v>
-      </c>
-      <c r="AE5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF5" s="39">
-        <v>11</v>
-      </c>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI5" s="39">
-        <v>12</v>
-      </c>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL5" s="39">
-        <v>13</v>
-      </c>
-      <c r="AM5" s="1"/>
-      <c r="AN5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO5" s="39">
-        <v>14</v>
-      </c>
-      <c r="AP5" s="1"/>
-      <c r="AQ5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AR5" s="39">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="58" t="str">
-        <f>IF(B5=-1,"SSR reduce",IF(B5=-2,"SSR hold",IF(B5=-3,"SSR elastic",_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="D6" s="58" t="str">
-        <f>IF(E5=-1,"SSR reduce",IF(E5=-2,"SSR hold",IF(E5=-3,"SSR elastic",_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="G6" s="58" t="str">
-        <f>IF(H5=-1,"SSR reduce",IF(H5=-2,"SSR hold",IF(H5=-3,"SSR elastic",_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="H6" s="57"/>
-      <c r="J6" s="58" t="str">
-        <f>IF(K5=-1,"SSR reduce",IF(K5=-2,"SSR hold",IF(K5=-3,"SSR elastic",_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="K6" s="57"/>
-      <c r="M6" s="58" t="str">
-        <f>IF(N5=-1,"SSR reduce",IF(N5=-2,"SSR hold",IF(N5=-3,"SSR elastic",_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="N6" s="57"/>
-      <c r="P6" s="58" t="str">
-        <f>IF(Q5=-1,"SSR reduce",IF(Q5=-2,"SSR hold",IF(Q5=-3,"SSR elastic",_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="58" t="str">
-        <f>IF(T5=-1,"SSR reduce",IF(T5=-2,"SSR hold",IF(T5=-3,"SSR elastic",_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="T6" s="57"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="58" t="str">
-        <f>IF(W5=-1,"SSR reduce",IF(W5=-2,"SSR hold",IF(W5=-3,"SSR elastic",_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="58" t="str">
-        <f>IF(Z5=-1,"SSR reduce",IF(Z5=-2,"SSR hold",IF(Z5=-3,"SSR elastic",_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="58" t="str">
-        <f>IF(AC5=-1,"SSR reduce",IF(AC5=-2,"SSR hold",IF(AC5=-3,"SSR elastic",_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="57"/>
-      <c r="AE6" s="58" t="str">
-        <f>IF(AF5=-1,"SSR reduce",IF(AF5=-2,"SSR hold",IF(AF5=-3,"SSR elastic",_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="57"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="58" t="str">
-        <f>IF(AI5=-1,"SSR reduce",IF(AI5=-2,"SSR hold",IF(AI5=-3,"SSR elastic",_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="58" t="str">
-        <f>IF(AL5=-1,"SSR reduce",IF(AL5=-2,"SSR hold",IF(AL5=-3,"SSR elastic",_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AL6" s="57"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="58" t="str">
-        <f>IF(AO5=-1,"SSR reduce",IF(AO5=-2,"SSR hold",IF(AO5=-3,"SSR elastic",_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AO6" s="57"/>
-      <c r="AP6" s="1"/>
-      <c r="AQ6" s="58" t="str">
-        <f>IF(AR5=-1,"SSR reduce",IF(AR5=-2,"SSR hold",IF(AR5=-3,"SSR elastic",_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
-        <v/>
-      </c>
-      <c r="AR6" s="57"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3"/>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="1"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3"/>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="1"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="1"/>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="3"/>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="1"/>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3"/>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="1"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="1"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="3"/>
-      <c r="AR14" s="3"/>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="1"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="1"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="1"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="1"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
-    </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="3"/>
-      <c r="AC20" s="3"/>
-      <c r="AE20" s="3"/>
-      <c r="AF20" s="3"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="3"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
-      <c r="AM20" s="1"/>
-      <c r="AN20" s="3"/>
-      <c r="AO20" s="3"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3"/>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="3"/>
-      <c r="AC22" s="3"/>
-      <c r="AE22" s="3"/>
-      <c r="AF22" s="3"/>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="3"/>
-      <c r="AI22" s="3"/>
-      <c r="AJ22" s="1"/>
-      <c r="AK22" s="3"/>
-      <c r="AL22" s="3"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="3"/>
-      <c r="AO22" s="3"/>
-      <c r="AP22" s="1"/>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="3"/>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="3"/>
-      <c r="AC23" s="3"/>
-      <c r="AE23" s="3"/>
-      <c r="AF23" s="3"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="3"/>
-      <c r="AI23" s="3"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="3"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="3"/>
-      <c r="AO23" s="3"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="3"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="3"/>
-      <c r="AC24" s="3"/>
-      <c r="AE24" s="3"/>
-      <c r="AF24" s="3"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="3"/>
-      <c r="AI24" s="3"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="3"/>
-      <c r="AL24" s="3"/>
-      <c r="AM24" s="1"/>
-      <c r="AN24" s="3"/>
-      <c r="AO24" s="3"/>
-      <c r="AP24" s="1"/>
-      <c r="AQ24" s="3"/>
-      <c r="AR24" s="3"/>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="3"/>
-      <c r="AC25" s="3"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="3"/>
-      <c r="AI25" s="3"/>
-      <c r="AJ25" s="1"/>
-      <c r="AK25" s="3"/>
-      <c r="AL25" s="3"/>
-      <c r="AM25" s="1"/>
-      <c r="AN25" s="3"/>
-      <c r="AO25" s="3"/>
-      <c r="AP25" s="1"/>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3"/>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="3"/>
-      <c r="AC26" s="3"/>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="3"/>
-      <c r="AG26" s="1"/>
-      <c r="AH26" s="3"/>
-      <c r="AI26" s="3"/>
-      <c r="AJ26" s="1"/>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-      <c r="AM26" s="1"/>
-      <c r="AN26" s="3"/>
-      <c r="AO26" s="3"/>
-      <c r="AP26" s="1"/>
-      <c r="AQ26" s="3"/>
-      <c r="AR26" s="3"/>
-    </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AE27" s="3"/>
-      <c r="AF27" s="3"/>
-      <c r="AG27" s="1"/>
-      <c r="AH27" s="3"/>
-      <c r="AI27" s="3"/>
-      <c r="AJ27" s="1"/>
-      <c r="AK27" s="3"/>
-      <c r="AL27" s="3"/>
-      <c r="AM27" s="1"/>
-      <c r="AN27" s="3"/>
-      <c r="AO27" s="3"/>
-      <c r="AP27" s="1"/>
-      <c r="AQ27" s="3"/>
-      <c r="AR27" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
-  </mergeCells>
+  <conditionalFormatting sqref="B6 A7:B7">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>AND($B$5&lt;&gt;"",$B$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6 D7:E7">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>AND($E$5&lt;&gt;"",$E$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6 G7:H7">
+    <cfRule type="expression" dxfId="15" priority="3">
+      <formula>AND($H$5&lt;&gt;"",$H$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6 J7:K7">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>AND($K$5&lt;&gt;"",$K$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N6 M7:N7">
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND($N$5&lt;&gt;"",$N$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6 P7:Q7">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>AND($Q$5&lt;&gt;"",$Q$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6 S7:T7">
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>AND($T$5&lt;&gt;"",$T$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W6 V7:W7">
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>AND($W$5&lt;&gt;"",$W$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6 Y7:Z7">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND($Z$5&lt;&gt;"",$Z$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6 AB7:AC7">
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND($AC$5&lt;&gt;"",$AC$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF6 AE7:AF7">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>AND($AF$5&lt;&gt;"",$AF$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI6 AH7:AI7">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>AND($AI$5&lt;&gt;"",$AI$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL6 AK7:AL7">
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>AND($AL$5&lt;&gt;"",$AL$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO6 AN7:AO7">
+    <cfRule type="expression" dxfId="4" priority="14">
+      <formula>AND($AO$5&lt;&gt;"",$AO$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AR6 AQ7:AR7">
+    <cfRule type="expression" dxfId="3" priority="15">
+      <formula>AND($AR$5&lt;&gt;"",$AR$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5 E5 H5 K5 N5 Q5 T5 W5 Z5 AC5 AF5 AI5 AL5 AO5 AR5" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"material,ssr reduce,ssr hold,ssr elastic,refine"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18007,17 +18503,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18192,7 +18688,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -18242,90 +18738,96 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3744.0</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
-        <v>200.0</v>
+        <v>0.0</v>
       </c>
       <c r="C5" s="3">
         <v>100.0</v>
@@ -18351,13 +18853,13 @@
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
-        <v>320.0</v>
+        <v>200.0</v>
       </c>
       <c r="C6" s="3">
-        <v>160.0</v>
+        <v>100.0</v>
       </c>
       <c r="D6" s="3">
-        <v>0.0</v>
+        <v>3744.0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -18376,9 +18878,15 @@
       <c r="X6" s="3"/>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>320.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>160.0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.0</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -18695,15 +19203,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/usage/sample_sheets/sheets_tseep.xlsx
+++ b/docs/usage/sample_sheets/sheets_tseep.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11708D50-B4AE-4447-916E-877A7873BC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1DA693-1E25-A64A-9652-172751DD72EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33220" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -223,6 +223,12 @@
     <t>Water loads:</t>
   </si>
   <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>Surface family:</t>
+  </si>
+  <si>
     <t>Unit Options:</t>
   </si>
   <si>
@@ -463,24 +469,9 @@
     <t>hb_d</t>
   </si>
   <si>
-    <t>s(g)</t>
-  </si>
-  <si>
-    <t>s(c)</t>
-  </si>
-  <si>
     <t>s(f)</t>
   </si>
   <si>
-    <t>s(c/p)</t>
-  </si>
-  <si>
-    <t>s(d)</t>
-  </si>
-  <si>
-    <t>s(psi)</t>
-  </si>
-  <si>
     <t>k1</t>
   </si>
   <si>
@@ -874,9 +865,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>qp</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -991,14 +979,153 @@
     <t>save_times</t>
   </si>
   <si>
-    <t>auto</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1114,6 +1241,13 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Symbol"/>
+      <charset val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1758,6 +1892,589 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>199571</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0FB8E9-E4E3-974A-BE46-8E599C58A56D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14804571" y="254001"/>
+          <a:ext cx="3610429" cy="3746499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Label</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1, y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>308429</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>117925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B716B0-439A-6440-8742-7BC140EF924C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14224000" y="190499"/>
+          <a:ext cx="3156858" cy="2521855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t> y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= top and bottom of pile</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>H</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:latin typeface="Symbol" pitchFamily="2" charset="2"/>
+            </a:rPr>
+            <a:t>q</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>p</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Force angle from horizontal in degrees (degrees)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pile diameter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = center to center pile spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Young's modulus of pile material (force/lengh^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>I </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Moment of inertia (length^4)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cross-sectional area (length^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fixity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile head status (fixed or free)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2314,21 +3031,27 @@
       <c r="C23" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>310</v>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
@@ -2338,22 +3061,22 @@
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
@@ -2363,7 +3086,7 @@
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D59" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -2373,89 +3096,89 @@
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D73" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
@@ -2477,6 +3200,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"circular,non-circular"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2497,67 +3223,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="H2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="I2" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="K2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="L2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Q2" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="Z2" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="AA2" t="s">
         <v>260</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>261</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -2588,13 +3314,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AA3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AB3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -2625,7 +3351,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -2656,7 +3382,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -2743,13 +3469,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AA8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AB8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -2780,13 +3506,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AA9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AB9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -2817,13 +3543,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AA10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AB10" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -2854,13 +3580,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AA11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AB11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -3174,7 +3900,7 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="T23" s="42"/>
       <c r="U23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -3182,7 +3908,7 @@
       <c r="L24" s="9"/>
       <c r="T24" s="26"/>
       <c r="U24" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -3190,7 +3916,7 @@
       <c r="L25" s="9"/>
       <c r="T25" s="29"/>
       <c r="U25" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3206,6 +3932,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3224,61 +3951,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="I2" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="J2" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="M2" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="N2" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="O2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="P2" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="L2" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="P2" s="28" t="s">
+      <c r="Z2" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA2" t="s">
         <v>261</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -3302,10 +4029,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AA3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -3508,19 +4235,19 @@
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="S16" s="42"/>
       <c r="T16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
       <c r="S17" s="26"/>
       <c r="T17" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="19:20" x14ac:dyDescent="0.2">
       <c r="S18" s="29"/>
       <c r="T18" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3533,6 +4260,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3548,22 +4276,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3786,27 +4514,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -3830,63 +4558,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -3915,10 +4643,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -3947,7 +4675,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4240,27 +4968,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4284,63 +5012,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4369,10 +5097,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4702,13 +5430,13 @@
         </is>
       </c>
       <c r="E2" s="50" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4723,7 +5451,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J3" s="3">
         <v>40.0</v>
@@ -4757,7 +5485,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J5" s="3">
         <v>5.0</v>
@@ -4791,7 +5519,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J7" s="3">
         <v>0.0</v>
@@ -4805,7 +5533,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J8" s="3">
         <v>20.0</v>
@@ -4819,7 +5547,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5667,123 +6395,123 @@
   <sheetData>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AJ2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AJ3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4" s="42"/>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD4" s="14"/>
       <c r="AJ4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -5809,7 +6537,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -5817,7 +6545,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -5834,127 +6562,127 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K10" s="49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="P10" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="S10" s="44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="T10" s="44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="U10" s="44" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="W10" s="44" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="X10" s="44" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Y10" s="44" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>308</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>135</v>
+        <v>307</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>136</v>
       </c>
       <c r="AD10" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>311</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AE10" s="46" t="s">
+      <c r="AH10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AF10" s="47" t="s">
+      <c r="AI10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>146</v>
-      </c>
-      <c r="AN10" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -7681,16 +8409,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -7713,157 +8441,157 @@
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -7956,172 +8684,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -8995,27 +9723,27 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9049,277 +9777,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Z5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AF5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AI5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AO5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AR5" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9412,172 +10140,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10382,36 +11110,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="V7:W7"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -10508,20 +11236,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -10529,7 +11257,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -10540,19 +11268,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -10565,7 +11293,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10574,10 +11302,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -10714,31 +11442,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -10766,10 +11494,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -10784,10 +11512,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -10802,10 +11530,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -10832,7 +11560,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -10847,7 +11575,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K8"/>
     </row>
@@ -10863,7 +11591,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K9"/>
     </row>
@@ -10879,7 +11607,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K10"/>
     </row>
@@ -10895,7 +11623,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K11"/>
     </row>
@@ -10911,31 +11639,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -10944,7 +11672,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K17"/>
     </row>
@@ -10985,16 +11713,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11005,10 +11733,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11016,10 +11744,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11027,10 +11755,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11160,134 +11888,128 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3744.0</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -11305,15 +12027,9 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B8" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3744.0</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -11331,15 +12047,9 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B9" s="3">
-        <v>320.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>160.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -11678,18 +12388,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -11727,134 +12437,128 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>624.0</v>
-      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -11872,15 +12576,9 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B8" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>624.0</v>
-      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -11898,15 +12596,9 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B9" s="3">
-        <v>220.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>110.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -12245,18 +12937,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0800-000000000000}">

--- a/docs/usage/sample_sheets/sheets_tseep.xlsx
+++ b/docs/usage/sample_sheets/sheets_tseep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1DA693-1E25-A64A-9652-172751DD72EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B93A9E-8BB4-7F49-AFDD-09E330D60C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -403,9 +403,6 @@
     <t>g</t>
   </si>
   <si>
-    <t>gsat</t>
-  </si>
-  <si>
     <t>option</t>
   </si>
   <si>
@@ -1118,6 +1115,25 @@
         <charset val="2"/>
       </rPr>
       <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
     </r>
   </si>
 </sst>
@@ -3223,67 +3239,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="Q2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="Z2" t="s">
         <v>258</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>259</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>260</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -3314,13 +3330,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA3" t="s">
         <v>262</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>263</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -3351,7 +3367,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -3382,7 +3398,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -3469,13 +3485,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA8" t="s">
         <v>259</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>260</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -3506,13 +3522,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA9" t="s">
         <v>262</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>263</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -3543,13 +3559,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -3580,13 +3596,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AA11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -3951,61 +3967,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>247</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="N2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="O2" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="N2" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="O2" s="28" t="s">
+      <c r="P2" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="P2" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>273</v>
-      </c>
       <c r="Z2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -4029,10 +4045,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -4276,22 +4292,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="E2" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4514,27 +4530,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4558,63 +4574,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4643,10 +4659,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U5" t="s">
         <v>285</v>
-      </c>
-      <c r="U5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4675,7 +4691,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4968,27 +4984,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5012,63 +5028,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5097,10 +5113,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U5" t="s">
         <v>285</v>
-      </c>
-      <c r="U5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5430,13 +5446,13 @@
         </is>
       </c>
       <c r="E2" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="50" t="s">
         <v>297</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>298</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5451,7 +5467,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J3" s="3">
         <v>40.0</v>
@@ -5485,7 +5501,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J5" s="3">
         <v>5.0</v>
@@ -5519,7 +5535,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J7" s="3">
         <v>0.0</v>
@@ -5533,7 +5549,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J8" s="3">
         <v>20.0</v>
@@ -5547,7 +5563,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -6568,121 +6584,121 @@
         <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="O10" s="44" t="s">
-        <v>125</v>
       </c>
       <c r="P10" s="44" t="s">
         <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="R10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AE10" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -8409,16 +8425,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>148</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8441,157 +8457,157 @@
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8684,172 +8700,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9714,6 +9730,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -9730,20 +9760,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9777,277 +9793,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -10140,172 +10156,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11110,16 +11126,10 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AK7:AL7"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
@@ -11136,10 +11146,16 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AK4:AL4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11236,20 +11252,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11257,7 +11273,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11268,19 +11284,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11293,7 +11309,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11302,10 +11318,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" t="s">
         <v>193</v>
-      </c>
-      <c r="H6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11442,31 +11458,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11494,10 +11510,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11512,10 +11528,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11530,10 +11546,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K5" t="s">
         <v>207</v>
-      </c>
-      <c r="K5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11560,7 +11576,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11575,7 +11591,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11591,7 +11607,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11607,7 +11623,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11623,7 +11639,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11639,31 +11655,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11672,7 +11688,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11713,16 +11729,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>222</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11733,10 +11749,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" t="s">
         <v>223</v>
-      </c>
-      <c r="F3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11744,10 +11760,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F4" t="s">
         <v>225</v>
-      </c>
-      <c r="F4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11755,10 +11771,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" t="s">
         <v>227</v>
-      </c>
-      <c r="F5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11888,122 +11904,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12437,122 +12453,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">

--- a/docs/usage/sample_sheets/sheets_tseep.xlsx
+++ b/docs/usage/sample_sheets/sheets_tseep.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B93A9E-8BB4-7F49-AFDD-09E330D60C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -343,9 +343,6 @@
     <t>vg</t>
   </si>
   <si>
-    <t>van Genuchten model (a, n)</t>
-  </si>
-  <si>
     <t>pow</t>
   </si>
   <si>
@@ -877,9 +874,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Fixity</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -974,28 +968,6 @@
   </si>
   <si>
     <t>save_times</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>p</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1136,12 +1108,42 @@
       <t>sat</t>
     </r>
   </si>
+  <si>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1257,13 +1259,6 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Symbol"/>
-      <charset val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1912,16 +1907,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1936,8 +1931,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2061,6 +2056,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2107,6 +2127,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2120,15 +2144,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
+      <xdr:colOff>553358</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>117925</xdr:rowOff>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2143,8 +2167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14224000" y="190499"/>
-          <a:ext cx="3156858" cy="2521855"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2200,34 +2224,15 @@
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
             <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-              <a:latin typeface="Symbol" pitchFamily="2" charset="2"/>
-            </a:rPr>
-            <a:t>q</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>p</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Force angle from horizontal in degrees (degrees)</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -2468,7 +2473,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2480,8 +2485,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2808,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -2833,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3013,7 +3064,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -3025,7 +3076,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -3037,28 +3088,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3100,93 +3157,98 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="1" t="s">
-        <v>62</v>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D62" s="1" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="1" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3195,28 +3257,28 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$D$54:$D$57</formula1>
+      <formula1>$D$54:$D$58</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>$D$60:$D$61</formula1>
+      <formula1>$D$61:$D$62</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$D$64:$D$71</formula1>
+      <formula1>$D$65:$D$72</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$D$74:$D$78</formula1>
+      <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3226,83 +3288,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3313,11 +3381,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3329,17 +3397,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3366,11 +3436,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3397,11 +3469,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3428,8 +3502,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3456,8 +3532,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3484,17 +3562,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3521,17 +3601,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3558,17 +3640,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>262</v>
-      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3595,17 +3679,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>262</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3632,8 +3718,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3660,8 +3748,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3688,8 +3778,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3716,8 +3808,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3744,8 +3838,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3772,8 +3868,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3800,8 +3898,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3828,8 +3928,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3856,8 +3958,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3884,8 +3988,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3912,39 +4018,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
-        <v>104</v>
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3954,74 +4062,74 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
     <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>249</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
       <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="N2" s="28" t="s">
-        <v>122</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="Z2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AA2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -4045,10 +4153,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="AA3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -4071,6 +4179,9 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -4092,6 +4203,9 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -4241,38 +4355,34 @@
       <c r="Q12" s="3"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="42"/>
-      <c r="T16" t="s">
-        <v>91</v>
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="26"/>
+      <c r="S17" s="29"/>
       <c r="T17" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="29"/>
-      <c r="T18" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4292,22 +4402,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4530,27 +4640,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4574,63 +4684,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4659,10 +4769,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4691,7 +4801,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4984,27 +5094,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5028,63 +5138,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5113,10 +5223,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5446,13 +5556,13 @@
         </is>
       </c>
       <c r="E2" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5467,7 +5577,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3">
         <v>40.0</v>
@@ -5501,7 +5611,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3">
         <v>5.0</v>
@@ -5535,7 +5645,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3">
         <v>0.0</v>
@@ -5549,7 +5659,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3">
         <v>20.0</v>
@@ -5563,7 +5673,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -6400,16 +6510,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6424,7 +6534,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6445,7 +6555,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6467,67 +6577,67 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -6553,7 +6663,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -6561,7 +6671,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -6572,136 +6682,140 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF10" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>310</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -6737,7 +6851,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>200000.0</v>
       </c>
@@ -6823,13 +6939,16 @@
         <v>0.0</v>
       </c>
       <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AP11" s="3">
         <v>1e-05</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AQ11" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -6860,12 +6979,14 @@
         <v>0.0</v>
       </c>
       <c r="J12" s="3">
-        <v>500.0</v>
+        <v>250.0</v>
       </c>
       <c r="K12" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="L12" s="3"/>
+        <v>14.0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>30000.0</v>
       </c>
@@ -6951,13 +7072,16 @@
         <v>0.0</v>
       </c>
       <c r="AO12" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="AP12" s="19">
         <v>1e-05</v>
       </c>
-      <c r="AP12" s="19">
+      <c r="AQ12" s="19">
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -6988,12 +7112,14 @@
         <v>0.0</v>
       </c>
       <c r="J13" s="3">
-        <v>250.0</v>
+        <v>0.0</v>
       </c>
       <c r="K13" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="L13" s="3"/>
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M13" s="3">
         <v>50000.0</v>
       </c>
@@ -7079,13 +7205,16 @@
         <v>0.0</v>
       </c>
       <c r="AO13" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="AP13" s="19">
         <v>1e-05</v>
       </c>
-      <c r="AP13" s="19">
+      <c r="AQ13" s="19">
         <v>0.15</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -7130,8 +7259,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -7176,8 +7306,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -7222,8 +7353,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -7268,8 +7400,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7314,8 +7447,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7360,8 +7494,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7406,8 +7541,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7452,8 +7588,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7498,8 +7635,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7544,8 +7682,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7590,8 +7729,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7636,8 +7776,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7670,8 +7811,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7695,7 +7837,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7719,7 +7861,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7743,7 +7885,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7767,7 +7909,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7791,7 +7933,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8297,7 +8439,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8377,7 +8519,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8425,16 +8567,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8457,157 +8599,157 @@
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8700,172 +8842,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9793,277 +9935,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -10156,172 +10298,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11126,26 +11268,21 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AH7:AI7"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -11156,6 +11293,11 @@
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11252,20 +11394,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11273,7 +11415,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11284,19 +11426,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11309,7 +11451,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11318,10 +11460,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11458,31 +11600,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11493,10 +11635,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>280.0</v>
+        <v>275.0</v>
       </c>
       <c r="C3" s="3">
-        <v>270.0</v>
+        <v>235.0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -11504,16 +11646,16 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>50.0</v>
+        <v>75.0</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11528,10 +11670,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11546,10 +11688,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11576,7 +11718,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11591,7 +11733,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11607,7 +11749,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11623,7 +11765,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11639,7 +11781,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11655,31 +11797,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11688,7 +11830,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11729,16 +11871,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11749,10 +11891,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11760,10 +11902,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11771,10 +11913,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11898,128 +12040,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12447,128 +12589,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
